--- a/outputs/51586.xlsx
+++ b/outputs/51586.xlsx
@@ -65,7 +65,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -87,13 +87,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -161,19 +154,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,78 +422,78 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="21.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="21.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="b">
-        <f aca="false">MID(A2,5,LEN(A2)-4)=B2</f>
+        <f aca="false">EXACT(A2,"ABC "&amp;B2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="b">
-        <f aca="false">MID(A3,5,LEN(A3)-4)=B3</f>
+        <f aca="false">EXACT(A3,"ABC "&amp;B3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="4" t="b">
-        <f aca="false">MID(A4,5,LEN(A4)-4)=B4</f>
+        <f aca="false">EXACT(A4,"ABC "&amp;B4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="b">
-        <f aca="false">MID(A5,5,LEN(A5)-4)=B5</f>
+        <f aca="false">EXACT(A5,"ABC "&amp;B5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="b">
-        <f aca="false">MID(A6,5,LEN(A6)-4)=B6</f>
+        <f aca="false">EXACT(A6,"ABC "&amp;B6)</f>
         <v>1</v>
       </c>
     </row>

--- a/outputs/51586.xlsx
+++ b/outputs/51586.xlsx
@@ -89,10 +89,12 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <family val="0"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -166,7 +168,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,63 +440,63 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="b">
-        <f aca="false">EXACT(A2,"ABC "&amp;B2)</f>
-        <v>1</v>
+        <f aca="false">IF(ISNUMBER(SEARCH(B2,A2)),FALSE(),TRUE())</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="b">
-        <f aca="false">EXACT(A3,"ABC "&amp;B3)</f>
-        <v>0</v>
+        <f aca="false">IF(ISNUMBER(SEARCH(B3,A3)),FALSE(),TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="4" t="b">
-        <f aca="false">EXACT(A4,"ABC "&amp;B4)</f>
-        <v>0</v>
+        <f aca="false">IF(ISNUMBER(SEARCH(B4,A4)),FALSE(),TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="b">
-        <f aca="false">EXACT(A5,"ABC "&amp;B5)</f>
+        <f aca="false">IF(ISNUMBER(SEARCH(B5,A5)),FALSE(),TRUE())</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="b">
-        <f aca="false">EXACT(A6,"ABC "&amp;B6)</f>
-        <v>1</v>
+        <f aca="false">IF(ISNUMBER(SEARCH(B6,A6)),FALSE(),TRUE())</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
